--- a/config/路网字段属性映射关系.xlsx
+++ b/config/路网字段属性映射关系.xlsx
@@ -476,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>3.75</v>
